--- a/GERADOR DE DOCUMENTOS/SCRIPTS/DADOS MUNICÍPIOS.xlsx
+++ b/GERADOR DE DOCUMENTOS/SCRIPTS/DADOS MUNICÍPIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\GERADOR DE DOCUMENTOS\SCRIPTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{627CEDE0-66DC-4466-97EA-475A6BA88F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EE6802-8482-49FE-AEF2-5079DCFECCF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2771,6 +2771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2847,7 +2848,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -2897,7 +2898,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -3065,7 +3066,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3283,7 +3284,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -3333,7 +3334,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -3439,7 +3440,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -3545,7 +3546,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -3595,7 +3596,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -3645,7 +3646,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -3695,7 +3696,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -3807,7 +3808,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -3919,7 +3920,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -4025,7 +4026,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -4184,7 +4185,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -4346,7 +4347,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>46</v>
       </c>
@@ -4564,7 +4565,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -4620,7 +4621,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>51</v>
       </c>
@@ -4676,7 +4677,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>52</v>
       </c>
@@ -4726,7 +4727,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>53</v>
       </c>
@@ -4832,7 +4833,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>55</v>
       </c>
@@ -4882,7 +4883,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>56</v>
       </c>
@@ -4988,7 +4989,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>58</v>
       </c>
@@ -5156,7 +5157,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>61</v>
       </c>
@@ -5206,7 +5207,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>62</v>
       </c>
@@ -5256,7 +5257,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>63</v>
       </c>
@@ -5306,7 +5307,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>64</v>
       </c>
@@ -5418,7 +5419,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>66</v>
       </c>
@@ -5468,7 +5469,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>67</v>
       </c>
@@ -5518,7 +5519,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>68</v>
       </c>
@@ -5574,7 +5575,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>69</v>
       </c>
@@ -5680,7 +5681,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>71</v>
       </c>
@@ -5842,7 +5843,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>74</v>
       </c>
@@ -5948,7 +5949,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>76</v>
       </c>
@@ -5998,7 +5999,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>77</v>
       </c>
@@ -6048,7 +6049,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>78</v>
       </c>
@@ -6098,7 +6099,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>79</v>
       </c>
@@ -6154,7 +6155,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>80</v>
       </c>
@@ -6204,7 +6205,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>81</v>
       </c>
@@ -6260,7 +6261,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>82</v>
       </c>
@@ -6366,7 +6367,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>84</v>
       </c>
@@ -6416,7 +6417,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>85</v>
       </c>
@@ -6523,7 +6524,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R70" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R70" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="ABEL"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>